--- a/styles/styles.xlsx
+++ b/styles/styles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flexup0.sharepoint.com/sites/FlexUpSharedFolder/Shared Documents/Legal/Styles/styles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{B03146FB-B39C-4187-A8DA-49626FBC9375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02ABAA05-7FAE-4A89-BBDE-B58ACFFB5BD9}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{B03146FB-B39C-4187-A8DA-49626FBC9375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F235B35C-FF23-499C-83A5-A98907A24941}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{6AF5B7A2-C91E-4868-8B5D-CDD1E4182A17}"/>
   </bookViews>
@@ -275,9 +275,6 @@
     <t>#### &lt;text&gt;</t>
   </si>
   <si>
-    <t>## Section I. &lt;text&gt;</t>
-  </si>
-  <si>
     <t>### Article 1. &lt;text&gt;</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>12</t>
+  </si>
+  <si>
+    <t>Bold 12, left, underlined, centered</t>
   </si>
 </sst>
 </file>
@@ -1008,11 +1008,11 @@
     </row>
     <row r="9" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
@@ -1034,11 +1034,11 @@
     </row>
     <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>16</v>
@@ -1051,7 +1051,7 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M10" s="4">
         <v>6</v>
@@ -1068,7 +1068,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>16</v>
@@ -1096,7 +1096,7 @@
         <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>16</v>
@@ -1124,7 +1124,7 @@
         <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
@@ -1168,10 +1168,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
@@ -1208,7 +1208,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>8</v>
@@ -1250,7 +1250,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>16</v>
@@ -1292,7 +1292,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>16</v>
@@ -1334,7 +1334,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>16</v>
@@ -1392,7 +1392,7 @@
         <v>46</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>24</v>
@@ -1426,7 +1426,7 @@
         <v>46</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>23</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>22</v>
@@ -1516,7 +1516,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>40</v>
@@ -1558,14 +1558,14 @@
         <v>5</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>32</v>
@@ -1581,7 +1581,7 @@
         <v>0.75</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M26" s="4">
         <v>6</v>
@@ -1598,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>16</v>
@@ -1640,7 +1640,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>16</v>
@@ -1732,7 +1732,7 @@
         <v>53</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>54</v>
@@ -1766,7 +1766,7 @@
         <v>53</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>16</v>
@@ -1799,15 +1799,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="585e1850-a672-4c59-9766-e6f9b47acd25" xsi:nil="true"/>
@@ -1816,6 +1807,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2014,20 +2014,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83C9A5F7-7B5B-407C-8EEF-0A1EF343B4EB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{331E6862-8E9F-4011-AD50-43EF39F1C7AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="585e1850-a672-4c59-9766-e6f9b47acd25"/>
     <ds:schemaRef ds:uri="c94c4ac8-faf4-477a-b4e6-6adaeda6e30a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83C9A5F7-7B5B-407C-8EEF-0A1EF343B4EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
